--- a/tiflow-chargeitem/build/0.9.0/StructureDefinition-GEM-ERPCHRG-PR-Communication-ChargChangeReq.xlsx
+++ b/tiflow-chargeitem/build/0.9.0/StructureDefinition-GEM-ERPCHRG-PR-Communication-ChargChangeReq.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2276" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2267" uniqueCount="393">
   <si>
     <t>Property</t>
   </si>
@@ -496,13 +496,6 @@
     <t>Meta.security</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
     <t>Communication.meta.tag</t>
   </si>
   <si>
@@ -672,9 +665,6 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
-    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
-  </si>
-  <si>
     <t>Communication.instantiatesCanonical</t>
   </si>
   <si>
@@ -688,9 +678,6 @@
     <t>The URL pointing to a FHIR-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Communication.</t>
   </si>
   <si>
-    <t>see [Canonical References](http://hl7.org/fhir/R4/references.html#canonical)</t>
-  </si>
-  <si>
     <t>Event.instantiatesCanonical</t>
   </si>
   <si>
@@ -732,14 +719,7 @@
     <t>This must point to some sort of a 'Request' resource, such as CarePlan, CommunicationRequest, ServiceRequest, MedicationRequest, etc.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
     <t>Event.basedOn</t>
-  </si>
-  <si>
-    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
   </si>
   <si>
     <t>Communication.basedOn.id</t>
@@ -842,9 +822,6 @@
     <t>Part of this action.</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
     <t>Event.partOf</t>
   </si>
   <si>
@@ -920,9 +897,6 @@
     <t>Event.statusReason</t>
   </si>
   <si>
-    <t>CD</t>
-  </si>
-  <si>
     <t>Communication.category</t>
   </si>
   <si>
@@ -975,9 +949,6 @@
   </si>
   <si>
     <t>A channel that was used for this communication (e.g. email, fax).</t>
-  </si>
-  <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>Codes for communication mediums such as phone, fax, email, in person, etc.</t>
@@ -1272,13 +1243,7 @@
     <t>Additional notes or commentary about the communication by the sender, receiver or other interested parties.</t>
   </si>
   <si>
-    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
-  </si>
-  <si>
     <t>Event.note</t>
-  </si>
-  <si>
-    <t>Act</t>
   </si>
 </sst>
 </file>
@@ -1637,7 +1602,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="43.421875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="123.23828125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="38.5234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2961,7 +2926,7 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>98</v>
@@ -2973,15 +2938,15 @@
         <v>76</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>155</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3007,13 +2972,13 @@
         <v>146</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="N13" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>159</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3039,31 +3004,31 @@
         <v>76</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="Z13" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="Y13" t="s" s="2">
+      <c r="AA13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -3072,7 +3037,7 @@
         <v>78</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>98</v>
@@ -3084,15 +3049,15 @@
         <v>76</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>155</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3118,13 +3083,13 @@
         <v>128</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3174,7 +3139,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3200,10 +3165,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3226,16 +3191,16 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3261,31 +3226,31 @@
         <v>76</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3311,14 +3276,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3337,16 +3302,16 @@
         <v>76</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3396,7 +3361,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3417,19 +3382,19 @@
         <v>76</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3448,16 +3413,16 @@
         <v>76</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3507,7 +3472,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3528,15 +3493,15 @@
         <v>76</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3565,7 +3530,7 @@
         <v>108</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>110</v>
@@ -3606,19 +3571,19 @@
         <v>76</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3639,15 +3604,15 @@
         <v>76</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3673,16 +3638,16 @@
         <v>107</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>110</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>76</v>
@@ -3719,19 +3684,19 @@
         <v>76</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3752,15 +3717,15 @@
         <v>76</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3783,19 +3748,19 @@
         <v>87</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>76</v>
@@ -3844,7 +3809,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3853,27 +3818,27 @@
         <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>210</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3896,17 +3861,15 @@
         <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>215</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>76</v>
@@ -3955,7 +3918,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3970,21 +3933,21 @@
         <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4010,13 +3973,13 @@
         <v>128</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4066,7 +4029,7 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -4081,25 +4044,25 @@
         <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4118,16 +4081,16 @@
         <v>87</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4177,7 +4140,7 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -4186,27 +4149,27 @@
         <v>78</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>229</v>
+        <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>231</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4312,10 +4275,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4423,10 +4386,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4452,13 +4415,13 @@
         <v>100</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4508,7 +4471,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4517,7 +4480,7 @@
         <v>86</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>98</v>
@@ -4529,15 +4492,15 @@
         <v>76</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4563,13 +4526,13 @@
         <v>128</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4598,10 +4561,10 @@
         <v>150</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>76</v>
@@ -4619,7 +4582,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4640,15 +4603,15 @@
         <v>76</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4671,16 +4634,16 @@
         <v>87</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4730,7 +4693,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4739,7 +4702,7 @@
         <v>86</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>98</v>
@@ -4751,15 +4714,15 @@
         <v>76</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4785,13 +4748,13 @@
         <v>100</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4841,7 +4804,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4862,19 +4825,19 @@
         <v>76</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4893,17 +4856,15 @@
         <v>87</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>76</v>
@@ -4952,7 +4913,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4961,27 +4922,27 @@
         <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>229</v>
+        <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>231</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5004,17 +4965,15 @@
         <v>76</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>76</v>
@@ -5063,7 +5022,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5072,10 +5031,10 @@
         <v>78</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>229</v>
+        <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>76</v>
@@ -5084,15 +5043,15 @@
         <v>76</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>231</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5115,16 +5074,16 @@
         <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5132,7 +5091,7 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>76</v>
@@ -5150,13 +5109,13 @@
         <v>76</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>76</v>
@@ -5174,7 +5133,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>86</v>
@@ -5189,10 +5148,10 @@
         <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>76</v>
@@ -5200,14 +5159,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5226,16 +5185,16 @@
         <v>87</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5261,13 +5220,13 @@
         <v>76</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>76</v>
@@ -5285,7 +5244,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5294,27 +5253,27 @@
         <v>86</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>288</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5337,16 +5296,16 @@
         <v>76</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5372,13 +5331,13 @@
         <v>76</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>76</v>
@@ -5396,7 +5355,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5405,7 +5364,7 @@
         <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>98</v>
@@ -5414,18 +5373,18 @@
         <v>76</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>288</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5448,23 +5407,23 @@
         <v>87</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q35" t="s" s="2">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="R35" t="s" s="2">
         <v>76</v>
@@ -5485,13 +5444,13 @@
         <v>76</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>76</v>
@@ -5509,7 +5468,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5527,7 +5486,7 @@
         <v>76</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>76</v>
@@ -5535,10 +5494,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5561,17 +5520,15 @@
         <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>307</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>76</v>
@@ -5596,13 +5553,13 @@
         <v>76</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>76</v>
@@ -5620,7 +5577,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5629,7 +5586,7 @@
         <v>78</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>98</v>
@@ -5641,19 +5598,19 @@
         <v>76</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>288</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5672,17 +5629,15 @@
         <v>87</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>76</v>
@@ -5731,7 +5686,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5740,27 +5695,27 @@
         <v>86</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>229</v>
+        <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>231</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5783,16 +5738,16 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5818,13 +5773,13 @@
         <v>76</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>76</v>
@@ -5842,7 +5797,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -5851,7 +5806,7 @@
         <v>86</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>98</v>
@@ -5860,18 +5815,18 @@
         <v>76</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>288</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5894,16 +5849,16 @@
         <v>76</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5953,7 +5908,7 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -5962,27 +5917,27 @@
         <v>78</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>229</v>
+        <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>231</v>
+        <v>76</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6005,16 +5960,16 @@
         <v>87</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6064,7 +6019,7 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -6073,27 +6028,27 @@
         <v>86</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>229</v>
+        <v>98</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>231</v>
+        <v>76</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6116,13 +6071,13 @@
         <v>76</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6173,7 +6128,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6188,10 +6143,10 @@
         <v>98</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>76</v>
@@ -6199,10 +6154,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6225,13 +6180,13 @@
         <v>76</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6282,7 +6237,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6297,10 +6252,10 @@
         <v>98</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>76</v>
@@ -6308,10 +6263,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6334,17 +6289,15 @@
         <v>76</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>76</v>
@@ -6393,7 +6346,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6402,27 +6355,27 @@
         <v>78</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>229</v>
+        <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>231</v>
+        <v>76</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6528,10 +6481,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6639,10 +6592,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6668,13 +6621,13 @@
         <v>100</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6724,7 +6677,7 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -6733,7 +6686,7 @@
         <v>86</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>98</v>
@@ -6745,15 +6698,15 @@
         <v>76</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6779,13 +6732,13 @@
         <v>128</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6814,10 +6767,10 @@
         <v>150</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>76</v>
@@ -6835,7 +6788,7 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -6856,15 +6809,15 @@
         <v>76</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6887,16 +6840,16 @@
         <v>87</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6946,7 +6899,7 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -6955,7 +6908,7 @@
         <v>86</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>98</v>
@@ -6967,15 +6920,15 @@
         <v>76</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7001,13 +6954,13 @@
         <v>100</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7057,7 +7010,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7078,15 +7031,15 @@
         <v>76</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7109,17 +7062,15 @@
         <v>76</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>76</v>
@@ -7168,7 +7119,7 @@
         <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7177,27 +7128,27 @@
         <v>86</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>229</v>
+        <v>98</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>231</v>
+        <v>76</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7303,10 +7254,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7414,10 +7365,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7443,13 +7394,13 @@
         <v>100</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7499,7 +7450,7 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7508,7 +7459,7 @@
         <v>86</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>98</v>
@@ -7520,15 +7471,15 @@
         <v>76</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7554,13 +7505,13 @@
         <v>128</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7589,10 +7540,10 @@
         <v>150</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>76</v>
@@ -7610,7 +7561,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -7631,15 +7582,15 @@
         <v>76</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7662,16 +7613,16 @@
         <v>87</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7721,7 +7672,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7730,7 +7681,7 @@
         <v>86</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>98</v>
@@ -7742,15 +7693,15 @@
         <v>76</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7776,13 +7727,13 @@
         <v>100</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7832,7 +7783,7 @@
         <v>76</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -7853,15 +7804,15 @@
         <v>76</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7884,16 +7835,16 @@
         <v>87</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -7919,13 +7870,13 @@
         <v>76</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>76</v>
@@ -7943,7 +7894,7 @@
         <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -7952,27 +7903,27 @@
         <v>78</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>376</v>
+        <v>367</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7995,17 +7946,15 @@
         <v>87</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>76</v>
@@ -8054,7 +8003,7 @@
         <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8063,27 +8012,27 @@
         <v>78</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>229</v>
+        <v>98</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>382</v>
+        <v>373</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8106,13 +8055,13 @@
         <v>76</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8163,7 +8112,7 @@
         <v>76</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8172,7 +8121,7 @@
         <v>78</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>98</v>
@@ -8184,15 +8133,15 @@
         <v>76</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>104</v>
+        <v>76</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8298,10 +8247,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8371,16 +8320,16 @@
         <v>76</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="AF61" t="s" s="2">
         <v>114</v>
@@ -8409,14 +8358,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -8438,16 +8387,16 @@
         <v>107</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>110</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>76</v>
@@ -8496,7 +8445,7 @@
         <v>76</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -8517,15 +8466,15 @@
         <v>76</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8551,10 +8500,10 @@
         <v>100</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8605,7 +8554,7 @@
         <v>76</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>86</v>
@@ -8614,7 +8563,7 @@
         <v>86</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>98</v>
@@ -8626,15 +8575,15 @@
         <v>76</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>104</v>
+        <v>76</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8657,17 +8606,15 @@
         <v>76</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>401</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>76</v>
@@ -8716,7 +8663,7 @@
         <v>76</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -8725,19 +8672,19 @@
         <v>78</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>403</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
